--- a/debug/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Llama-3.1-8B-Instruct/simple/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Llama-3.1-8B-Instruct/simple/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>9</v>
+        <v>93</v>
       </c>
       <c r="D2">
-        <v>5</v>
+        <v>91</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>51</v>
       </c>
       <c r="G2">
-        <v>406</v>
+        <v>191</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>5</v>
+        <v>134</v>
       </c>
       <c r="D3">
-        <v>7</v>
+        <v>77</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c r="G3">
-        <v>408</v>
+        <v>170</v>
       </c>
       <c r="H3">
         <v>426</v>

--- a/debug/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Llama-3.1-8B-Instruct/simple/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Llama-3.1-8B-Instruct/simple/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="D2">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="E2">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="G2">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="D3">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="E3">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="G3">
-        <v>170</v>
+        <v>217</v>
       </c>
       <c r="H3">
         <v>426</v>
